--- a/data/trans_dic/P44A$analisis-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P44A$analisis-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado al menos un análisis de sangre para detectar cáncer de cólon</t>
+          <t>Población a la que le han realizado al menos un análisis de sangre para detectar cáncer de cólon (tasa de respuesta: 98,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>27,13; 56,9</t>
+          <t>26,64; 57,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20,01; 45,32</t>
+          <t>20,76; 45,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,2; 15,48</t>
+          <t>6,74; 15,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,15; 41,68</t>
+          <t>18,31; 41,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,81; 52,95</t>
+          <t>27,76; 54,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,03; 16,98</t>
+          <t>9,35; 17,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,42; 45,08</t>
+          <t>25,98; 44,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>27,48; 45,63</t>
+          <t>26,84; 45,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,22; 14,66</t>
+          <t>9,09; 15,0</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>20,05; 49,14</t>
+          <t>21,82; 49,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27,5; 49,8</t>
+          <t>26,9; 49,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,68; 87,25</t>
+          <t>14,81; 87,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,55; 55,84</t>
+          <t>19,09; 55,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,23; 44,85</t>
+          <t>14,89; 47,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,08; 15,55</t>
+          <t>8,87; 15,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,77; 47,47</t>
+          <t>24,05; 46,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>25,89; 44,31</t>
+          <t>26,73; 44,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,19; 76,32</t>
+          <t>13,33; 76,11</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,33; 67,75</t>
+          <t>12,82; 68,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23,84; 62,51</t>
+          <t>24,14; 59,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,78; 17,2</t>
+          <t>6,26; 17,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,91; 67,83</t>
+          <t>9,77; 67,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,53; 60,13</t>
+          <t>10,77; 61,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,33; 11,55</t>
+          <t>3,1; 10,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,26; 56,41</t>
+          <t>18,84; 57,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22,32; 53,45</t>
+          <t>21,16; 52,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,75; 12,88</t>
+          <t>6,05; 13,04</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,99; 47,61</t>
+          <t>27,93; 49,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,41; 44,63</t>
+          <t>29,11; 44,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,65; 74,88</t>
+          <t>12,44; 74,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,17; 42,61</t>
+          <t>23,25; 41,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,97; 45,02</t>
+          <t>24,66; 44,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,24; 13,41</t>
+          <t>9,3; 13,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,05; 41,9</t>
+          <t>27,6; 42,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30,31; 42,45</t>
+          <t>29,73; 41,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,83; 59,6</t>
+          <t>11,92; 63,15</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado al menos un análisis de sangre para detectar cáncer de cólon</t>
+          <t>Población a la que le han realizado al menos un análisis de sangre para detectar cáncer de cólon (tasa de respuesta: 98,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12223; 25637</t>
+          <t>12005; 25955</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10350; 23436</t>
+          <t>10737; 23679</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8714; 21744</t>
+          <t>9465; 21669</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11416; 26220</t>
+          <t>11517; 26355</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>16653; 32890</t>
+          <t>17240; 33879</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15340; 28847</t>
+          <t>15888; 28982</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27445; 48677</t>
+          <t>28055; 47700</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>31276; 51936</t>
+          <t>30547; 52049</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>28619; 45487</t>
+          <t>28227; 46570</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9973; 24447</t>
+          <t>10853; 24678</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21475; 38887</t>
+          <t>21004; 38715</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>74940; 445512</t>
+          <t>75625; 445404</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5038; 17000</t>
+          <t>5812; 16764</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5186; 16344</t>
+          <t>5426; 17302</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20239; 34678</t>
+          <t>19780; 34290</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19865; 38067</t>
+          <t>19284; 37168</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29645; 50748</t>
+          <t>30613; 50991</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>96733; 559915</t>
+          <t>97790; 558372</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1796; 9866</t>
+          <t>1867; 10004</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6901; 18092</t>
+          <t>6986; 17183</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8388; 21284</t>
+          <t>7740; 21033</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1112; 8471</t>
+          <t>1221; 8445</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1215; 9707</t>
+          <t>1739; 9950</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2833; 9835</t>
+          <t>2644; 9215</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4939; 15260</t>
+          <t>5098; 15639</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10065; 24097</t>
+          <t>9540; 23533</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12003; 26903</t>
+          <t>12630; 27237</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>30607; 52072</t>
+          <t>30546; 53643</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>46678; 70850</t>
+          <t>46210; 70195</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>97996; 580197</t>
+          <t>96392; 575108</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24522; 45100</t>
+          <t>24608; 44330</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>29791; 51638</t>
+          <t>28283; 51299</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>44190; 64092</t>
+          <t>44454; 64367</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>60376; 90172</t>
+          <t>59401; 90640</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>82881; 116076</t>
+          <t>81280; 112386</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>148249; 746725</t>
+          <t>149400; 791177</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P44A$analisis-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P44A$analisis-Estudios-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>12,08%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>26,64; 57,61</t>
+          <t>27,43; 59,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20,76; 45,79</t>
+          <t>21,5; 45,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,74; 15,43</t>
+          <t>6,95; 16,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,31; 41,89</t>
+          <t>18,12; 42,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>27,76; 54,54</t>
+          <t>26,85; 53,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,35; 17,06</t>
+          <t>9,51; 17,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,98; 44,18</t>
+          <t>25,66; 44,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>26,84; 45,73</t>
+          <t>26,9; 45,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,09; 15,0</t>
+          <t>9,39; 15,15</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>14,16%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,82; 49,61</t>
+          <t>20,26; 50,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26,9; 49,58</t>
+          <t>27,39; 50,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,81; 87,23</t>
+          <t>11,74; 19,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19,09; 55,07</t>
+          <t>16,79; 55,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,89; 47,48</t>
+          <t>14,96; 44,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,87; 15,38</t>
+          <t>8,9; 16,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,05; 46,35</t>
+          <t>22,85; 46,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>26,73; 44,52</t>
+          <t>25,84; 43,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,33; 76,11</t>
+          <t>11,5; 16,9</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,3%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,82; 68,69</t>
+          <t>13,51; 66,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24,14; 59,37</t>
+          <t>21,87; 59,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,26; 17,0</t>
+          <t>6,14; 16,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,77; 67,62</t>
+          <t>9,25; 67,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,77; 61,64</t>
+          <t>11,59; 62,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,1; 10,82</t>
+          <t>3,78; 11,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,84; 57,81</t>
+          <t>19,11; 59,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21,16; 52,19</t>
+          <t>23,85; 55,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,05; 13,04</t>
+          <t>6,26; 12,92</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,93; 49,05</t>
+          <t>28,55; 47,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,11; 44,22</t>
+          <t>29,02; 44,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,44; 74,22</t>
+          <t>10,61; 16,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,25; 41,88</t>
+          <t>23,3; 40,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,66; 44,72</t>
+          <t>24,19; 44,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,3; 13,46</t>
+          <t>9,68; 13,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,6; 42,12</t>
+          <t>28,39; 41,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>29,73; 41,1</t>
+          <t>30,2; 42,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,92; 63,15</t>
+          <t>10,97; 14,38</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14594</t>
+          <t>15917</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21820</t>
+          <t>24697</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>36414</t>
+          <t>40614</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12005; 25955</t>
+          <t>12360; 26843</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10737; 23679</t>
+          <t>11120; 23541</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9465; 21669</t>
+          <t>10396; 24111</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11517; 26355</t>
+          <t>11397; 26446</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17240; 33879</t>
+          <t>16676; 33461</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15888; 28982</t>
+          <t>17774; 32853</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28055; 47700</t>
+          <t>27710; 48360</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30547; 52049</t>
+          <t>30619; 51445</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>28227; 46570</t>
+          <t>31597; 50946</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>287159</t>
+          <t>45377</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26700</t>
+          <t>30327</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>313859</t>
+          <t>75704</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10853; 24678</t>
+          <t>10078; 25083</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21004; 38715</t>
+          <t>21385; 39459</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>75625; 445404</t>
+          <t>34024; 57496</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5812; 16764</t>
+          <t>5112; 16856</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5426; 17302</t>
+          <t>5450; 16359</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19780; 34290</t>
+          <t>21781; 39392</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19284; 37168</t>
+          <t>18322; 37287</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30613; 50991</t>
+          <t>29598; 49652</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>97790; 558372</t>
+          <t>61464; 90371</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13514</t>
+          <t>13986</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5403</t>
+          <t>7053</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18917</t>
+          <t>21040</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1867; 10004</t>
+          <t>1968; 9705</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6986; 17183</t>
+          <t>6330; 17284</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7740; 21033</t>
+          <t>7957; 21479</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1221; 8445</t>
+          <t>1155; 8383</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1739; 9950</t>
+          <t>1871; 10140</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2644; 9215</t>
+          <t>3648; 11550</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5098; 15639</t>
+          <t>5171; 16163</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9540; 23533</t>
+          <t>10752; 24810</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12630; 27237</t>
+          <t>14151; 29215</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>315266</t>
+          <t>75280</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53924</t>
+          <t>62077</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>369190</t>
+          <t>137357</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>30546; 53643</t>
+          <t>31229; 52413</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>46210; 70195</t>
+          <t>46065; 69951</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>96392; 575108</t>
+          <t>60347; 91760</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24608; 44330</t>
+          <t>24662; 43058</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>28283; 51299</t>
+          <t>27746; 50767</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>44454; 64367</t>
+          <t>51114; 73872</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>59401; 90640</t>
+          <t>61098; 88984</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>81280; 112386</t>
+          <t>82579; 115764</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>149400; 791177</t>
+          <t>120305; 157802</t>
         </is>
       </c>
     </row>
